--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15159,7 +15159,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -15945,7 +15945,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -28128,7 +28128,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28521,7 +28521,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29307,7 +29307,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29700,7 +29700,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -30093,7 +30093,7 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30879,7 +30879,7 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -31272,7 +31272,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31665,7 +31665,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -42276,7 +42276,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -43062,7 +43062,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43455,7 +43455,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -44241,7 +44241,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44634,7 +44634,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -45027,7 +45027,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45813,7 +45813,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46206,7 +46206,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -57603,7 +57603,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -57996,7 +57996,7 @@
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -58389,7 +58389,7 @@
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -58782,7 +58782,7 @@
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -59175,7 +59175,7 @@
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -59568,7 +59568,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -59961,7 +59961,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60354,7 +60354,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -60747,7 +60747,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -61140,7 +61140,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -61926,7 +61926,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -72930,7 +72930,7 @@
       </c>
       <c r="AM369" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN369" t="b">
@@ -73323,7 +73323,7 @@
       </c>
       <c r="AM371" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN371" t="b">
@@ -73716,7 +73716,7 @@
       </c>
       <c r="AM373" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN373" t="b">
@@ -74109,7 +74109,7 @@
       </c>
       <c r="AM375" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN375" t="b">
@@ -74502,7 +74502,7 @@
       </c>
       <c r="AM377" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN377" t="b">
@@ -74895,7 +74895,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -75288,7 +75288,7 @@
       </c>
       <c r="AM381" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN381" t="b">
@@ -75681,7 +75681,7 @@
       </c>
       <c r="AM383" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN383" t="b">
@@ -76074,7 +76074,7 @@
       </c>
       <c r="AM385" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN385" t="b">
@@ -76467,7 +76467,7 @@
       </c>
       <c r="AM387" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN387" t="b">
@@ -76860,7 +76860,7 @@
       </c>
       <c r="AM389" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN389" t="b">

--- a/diseases/d167/2015-2019.xlsx
+++ b/diseases/d167/2015-2019.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27725,7 +27725,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28118,7 +28118,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28511,7 +28511,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28904,7 +28904,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29297,7 +29297,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -29690,7 +29690,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30083,7 +30083,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -30476,7 +30476,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31262,7 +31262,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -31655,7 +31655,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -42266,7 +42266,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -43052,7 +43052,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -43838,7 +43838,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -44231,7 +44231,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -44624,7 +44624,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -45410,7 +45410,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -57593,7 +57593,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -57986,7 +57986,7 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
@@ -58379,7 +58379,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -58772,7 +58772,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -59165,7 +59165,7 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
@@ -59558,7 +59558,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -59951,7 +59951,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60344,7 +60344,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60737,7 +60737,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61130,7 +61130,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -61523,7 +61523,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61916,7 +61916,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -72920,7 +72920,7 @@
       </c>
       <c r="AJ369" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK369" t="inlineStr">
@@ -73313,7 +73313,7 @@
       </c>
       <c r="AJ371" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK371" t="inlineStr">
@@ -73706,7 +73706,7 @@
       </c>
       <c r="AJ373" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK373" t="inlineStr">
@@ -74099,7 +74099,7 @@
       </c>
       <c r="AJ375" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK375" t="inlineStr">
@@ -74492,7 +74492,7 @@
       </c>
       <c r="AJ377" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK377" t="inlineStr">
@@ -74885,7 +74885,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -75278,7 +75278,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -75671,7 +75671,7 @@
       </c>
       <c r="AJ383" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK383" t="inlineStr">
@@ -76064,7 +76064,7 @@
       </c>
       <c r="AJ385" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK385" t="inlineStr">
@@ -76457,7 +76457,7 @@
       </c>
       <c r="AJ387" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK387" t="inlineStr">
@@ -76850,7 +76850,7 @@
       </c>
       <c r="AJ389" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK389" t="inlineStr">
